--- a/resources/tool_obs_community_iphra_v2.xlsx
+++ b/resources/tool_obs_community_iphra_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16343B95-04B1-4A96-9E35-CC97B2141275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D66D22E-9A99-41BA-A841-2B6103AC6C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{27C29DD6-0256-4DF1-82F8-B613F9F4F125}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -40,26 +40,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={ACB7281F-A5FF-4C05-9A6A-08303A5049D9}</author>
-  </authors>
-  <commentList>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{ACB7281F-A5FF-4C05-9A6A-08303A5049D9}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Proposing these changes to source types, because previous options did not unable to easily classify improved vs. unimproved facilities. Please let me know what you think.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="124">
   <si>
     <t>type</t>
   </si>
@@ -190,231 +172,9 @@
     <t>(Tap detect current location icon)</t>
   </si>
   <si>
-    <t>water_points</t>
-  </si>
-  <si>
-    <t>hand_dug</t>
-  </si>
-  <si>
-    <t>borehole</t>
-  </si>
-  <si>
-    <t>water_trucking</t>
-  </si>
-  <si>
-    <t>Other, specify</t>
-  </si>
-  <si>
-    <t>source</t>
-  </si>
-  <si>
-    <t>surface_water</t>
-  </si>
-  <si>
-    <t>rain_water</t>
-  </si>
-  <si>
-    <t>underground_water</t>
-  </si>
-  <si>
-    <t>Surface water</t>
-  </si>
-  <si>
-    <t>Rain water</t>
-  </si>
-  <si>
-    <t>Underground water</t>
-  </si>
-  <si>
-    <t>Water trucking</t>
-  </si>
-  <si>
-    <t>power</t>
-  </si>
-  <si>
-    <t>solar</t>
-  </si>
-  <si>
-    <t>generator</t>
-  </si>
-  <si>
-    <t>combined</t>
-  </si>
-  <si>
-    <t>electricity</t>
-  </si>
-  <si>
-    <t>manual</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Generator</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t>Combined (Dual-Source)</t>
-  </si>
-  <si>
-    <t>distribution</t>
-  </si>
-  <si>
-    <t>piped_to_households</t>
-  </si>
-  <si>
-    <t>communal_tap</t>
-  </si>
-  <si>
-    <t>stored_in_tank</t>
-  </si>
-  <si>
-    <t>bucket_rope</t>
-  </si>
-  <si>
-    <t>jerry_cans_buckets</t>
-  </si>
-  <si>
-    <t>Piped system to households</t>
-  </si>
-  <si>
-    <t>Communal tap stands</t>
-  </si>
-  <si>
-    <t>Stored in tank</t>
-  </si>
-  <si>
-    <t>Bucket and rope</t>
-  </si>
-  <si>
-    <t>Jerry cans or buckets</t>
-  </si>
-  <si>
-    <t>soil</t>
-  </si>
-  <si>
-    <t>rock_gravel</t>
-  </si>
-  <si>
-    <t>clay</t>
-  </si>
-  <si>
-    <t>silt_fineearth</t>
-  </si>
-  <si>
-    <t>sand_sediment</t>
-  </si>
-  <si>
     <t>dont_know</t>
   </si>
   <si>
-    <t>Rock/Gravel</t>
-  </si>
-  <si>
-    <t>Clay</t>
-  </si>
-  <si>
-    <t>Silt/ Fine Earth</t>
-  </si>
-  <si>
-    <t>Sand/ Sediment</t>
-  </si>
-  <si>
-    <t>Don't Know</t>
-  </si>
-  <si>
-    <t>yield</t>
-  </si>
-  <si>
-    <t>Flow Meter Reading or Volumetric Measurements reported by WASH partner</t>
-  </si>
-  <si>
-    <t>Manual Measurement (Bucket)</t>
-  </si>
-  <si>
-    <t>No Equipment to Measure the Yield</t>
-  </si>
-  <si>
-    <t>Don’t Know</t>
-  </si>
-  <si>
-    <t>flow_meter_volumetric</t>
-  </si>
-  <si>
-    <t>manual_bucket</t>
-  </si>
-  <si>
-    <t>no_equipment</t>
-  </si>
-  <si>
-    <t>rehab_waterpoint</t>
-  </si>
-  <si>
-    <t>Cleaning and desludging</t>
-  </si>
-  <si>
-    <t>Structural repairs</t>
-  </si>
-  <si>
-    <t>Coating and lining</t>
-  </si>
-  <si>
-    <t>Replacing tank components</t>
-  </si>
-  <si>
-    <t>cleaning_desludging</t>
-  </si>
-  <si>
-    <t>structural_repairs</t>
-  </si>
-  <si>
-    <t>coating_lining</t>
-  </si>
-  <si>
-    <t>replacing_tank_components</t>
-  </si>
-  <si>
-    <t>rehab_network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well development </t>
-  </si>
-  <si>
-    <t>Well head construction</t>
-  </si>
-  <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
-    <t>Installation Lifting Devices with Power Sources</t>
-  </si>
-  <si>
-    <t>Water Tanks</t>
-  </si>
-  <si>
-    <t>Water points</t>
-  </si>
-  <si>
-    <t>well_development</t>
-  </si>
-  <si>
-    <t>well_head_construction</t>
-  </si>
-  <si>
-    <t>pipeline</t>
-  </si>
-  <si>
-    <t>installation_lifting_devices</t>
-  </si>
-  <si>
-    <t>water_tanks</t>
-  </si>
-  <si>
     <t>repeat_count</t>
   </si>
   <si>
@@ -422,51 +182,6 @@
   </si>
   <si>
     <t xml:space="preserve">Is there any other comment or observation on the status or quality of this water point? </t>
-  </si>
-  <si>
-    <t>spring_protected</t>
-  </si>
-  <si>
-    <t>spring_unprotected</t>
-  </si>
-  <si>
-    <t>Protected Spring</t>
-  </si>
-  <si>
-    <t>Borehole / Protected well</t>
-  </si>
-  <si>
-    <t>Hand dug well / Unprotected well</t>
-  </si>
-  <si>
-    <t>Unprotected Spring</t>
-  </si>
-  <si>
-    <t>reservoir</t>
-  </si>
-  <si>
-    <t>Reservoir / Tank</t>
-  </si>
-  <si>
-    <t>Desalinated water</t>
-  </si>
-  <si>
-    <t>desalination</t>
-  </si>
-  <si>
-    <t>flow_unit</t>
-  </si>
-  <si>
-    <t>liters_per_min</t>
-  </si>
-  <si>
-    <t>liters_per_sec</t>
-  </si>
-  <si>
-    <t>Liters per Second</t>
-  </si>
-  <si>
-    <t>Liters per Minute</t>
   </si>
   <si>
     <t>indicator_code</t>
@@ -566,17 +281,164 @@
     <t>Please provide GPS coordinates of the starting location</t>
   </si>
   <si>
-    <t>41004, 58002, 59201</t>
-  </si>
-  <si>
     <t>biological_chemical_threats</t>
+  </si>
+  <si>
+    <t>13204, 15102, 15401</t>
+  </si>
+  <si>
+    <t>yes_no_dnk</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Don't know</t>
+  </si>
+  <si>
+    <t>Ne sait pas</t>
+  </si>
+  <si>
+    <t>yes_no_dnk_pnta</t>
+  </si>
+  <si>
+    <t>prefer_not_to_answer</t>
+  </si>
+  <si>
+    <t>Decline to answer</t>
+  </si>
+  <si>
+    <t>Préfère ne pas répondre</t>
+  </si>
+  <si>
+    <t>yes_no_other</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Autre</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>admin1a</t>
+  </si>
+  <si>
+    <t>To be updated by country</t>
+  </si>
+  <si>
+    <t>À mettre à jour par le pays</t>
+  </si>
+  <si>
+    <t>admin1b</t>
+  </si>
+  <si>
+    <t>admin1c</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>admin2a</t>
+  </si>
+  <si>
+    <t>admin2b</t>
+  </si>
+  <si>
+    <t>admin2c</t>
+  </si>
+  <si>
+    <t>admin3</t>
+  </si>
+  <si>
+    <t>admin3a</t>
+  </si>
+  <si>
+    <t>admin3b</t>
+  </si>
+  <si>
+    <t>admin3c</t>
+  </si>
+  <si>
+    <t>admin4</t>
+  </si>
+  <si>
+    <t>admin4a</t>
+  </si>
+  <si>
+    <t>admin4b</t>
+  </si>
+  <si>
+    <t>admin4c</t>
+  </si>
+  <si>
+    <t>label::French (fr)</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>Team 1</t>
+  </si>
+  <si>
+    <t>Équipe 1</t>
+  </si>
+  <si>
+    <t>Team 2</t>
+  </si>
+  <si>
+    <t>Équipe 2</t>
+  </si>
+  <si>
+    <t>Team 3</t>
+  </si>
+  <si>
+    <t>Équipe 3</t>
+  </si>
+  <si>
+    <t>Team 4</t>
+  </si>
+  <si>
+    <t>Équipe 4</t>
+  </si>
+  <si>
+    <t>Team 5</t>
+  </si>
+  <si>
+    <t>Équipe 5</t>
+  </si>
+  <si>
+    <t>Homme</t>
+  </si>
+  <si>
+    <t>Femme</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -596,6 +458,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -619,7 +487,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -636,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -652,12 +520,106 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -682,9 +644,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Emma KRUGER" id="{A9E24A12-962C-4CD7-9795-7036DFAD00E1}" userId="S::emma.kruger@impact-initiatives.org::60665a82-bfe7-4fa3-be8e-fe4563e83caf" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1002,14 +962,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A4" dT="2025-07-09T10:14:10.04" personId="{A9E24A12-962C-4CD7-9795-7036DFAD00E1}" id="{ACB7281F-A5FF-4C05-9A6A-08303A5049D9}">
-    <text>Proposing these changes to source types, because previous options did not unable to easily classify improved vs. unimproved facilities. Please let me know what you think.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2A72A4-B69F-42B0-BA64-020C51FE6931}">
   <dimension ref="A1:M99"/>
@@ -1028,7 +980,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1064,7 +1016,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1208,7 +1160,7 @@
         <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -1218,164 +1170,164 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="90" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>61006</v>
+      <c r="A11" s="8">
+        <v>15606</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>43001</v>
+      <c r="A12" s="8">
+        <v>13401</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="F12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>32105</v>
+      <c r="A13" s="8">
+        <v>12307</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="90" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>162</v>
+      <c r="A14" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>143</v>
+        <v>54</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>56001</v>
+      <c r="A15" s="8">
+        <v>14701</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="90" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>56002</v>
+      <c r="A16" s="8">
+        <v>14702</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="F16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="90" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>56003</v>
+      <c r="A17" s="8">
+        <v>14703</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="F17" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1386,19 +1338,19 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="F18" s="2" t="b">
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1409,10 +1361,10 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98" spans="3:4" x14ac:dyDescent="0.25">
@@ -1428,601 +1380,579 @@
   </sheetData>
   <autoFilter ref="B1:M19" xr:uid="{6D2A72A4-B69F-42B0-BA64-020C51FE6931}"/>
   <conditionalFormatting sqref="C8:C9">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
-  <dimension ref="A1:I52"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D63B81B-C0DE-4D5C-B8D8-1821B93262B2}">
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="2"/>
+    <col min="1" max="1" width="25.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="42.85546875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="E1" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="8" t="s">
+    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="9">
+        <v>3</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="9">
+        <v>4</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="9">
+        <v>5</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="2" t="s">
+    </row>
+    <row r="21" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="E21" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    </row>
+    <row r="22" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D22" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="C23" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="D23" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="C27" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="D27" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="D28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="D29" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="C30" s="9" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="D30" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="D31" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="C32" s="9" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>134</v>
+      <c r="D32" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C4:C6">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C10">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C12">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:C32">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:C20">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2062,6 +1992,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
     <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
@@ -2302,27 +2252,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A28B40-7C99-42AA-A812-F7E1B312E52E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c"/>
+    <ds:schemaRef ds:uri="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6"/>
+    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
+    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD810D2-AE12-44E9-9666-8142EEC15392}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D17A2946-34CC-446E-B90E-BB649BEB931E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2339,25 +2290,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD810D2-AE12-44E9-9666-8142EEC15392}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30A28B40-7C99-42AA-A812-F7E1B312E52E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e7a156ab-dec1-49fa-a9cf-4ddad9eb4e7c"/>
-    <ds:schemaRef ds:uri="7a5b9cf8-6f84-47d8-bb23-7f0863df71c6"/>
-    <ds:schemaRef ds:uri="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
-    <ds:schemaRef ds:uri="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>